--- a/lake_monitoring_for_report_appendix.xlsx
+++ b/lake_monitoring_for_report_appendix.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t xml:space="preserve">Waterbody</t>
   </si>
@@ -38,130 +38,160 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Allison Lake</t>
+    <t xml:space="preserve">Alouette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower Mainland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLWRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrow Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kootenay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baynes Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKISC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cariboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bull River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kootenay, Kootenay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKISC, EKISC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA, no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burnaby Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCMV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canim Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedar Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champion Lakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilliwack River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FVISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christina Lake</t>
   </si>
   <si>
     <t xml:space="preserve">Okanagan</t>
   </si>
   <si>
+    <t xml:space="preserve">CLSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbia River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKISS, CSISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no, no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultus Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deer Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deka Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duncan Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erie Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francois Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skeena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horse Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horsefly Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illecillewaet River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jewel Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jim Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jim Smith Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jimsmith Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalamalka Lake</t>
+  </si>
+  <si>
     <t xml:space="preserve">OASISS</t>
   </si>
   <si>
-    <t xml:space="preserve">Alouette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lower Mainland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLWRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrow Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kootenay, Kootenay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKISS, CSISS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no, no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baynes Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kootenay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKISC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridge Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cariboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridge River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRISS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bull River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canim Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cedar Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Champion Lakes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christina Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kootenay, Okanagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLSS, CLSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columbia River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultus Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FVISS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deka Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duncan Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKISS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horse Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horsefly Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jim Smith Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalamalka Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamloops Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WLRS</t>
+    <t xml:space="preserve">Kicking Horse River</t>
   </si>
   <si>
     <t xml:space="preserve">Kinbasket Lake</t>
@@ -182,30 +212,18 @@
     <t xml:space="preserve">Lac la Hache</t>
   </si>
   <si>
-    <t xml:space="preserve">Lac le Jeune</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lake Enid</t>
   </si>
   <si>
-    <t xml:space="preserve">Lake Windemere</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lazy Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Leighton</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lillian Lake</t>
   </si>
   <si>
     <t xml:space="preserve">Little Shuswap Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Logan Lake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Loon Lake</t>
   </si>
   <si>
@@ -215,9 +233,6 @@
     <t xml:space="preserve">Lower Kettle River</t>
   </si>
   <si>
-    <t xml:space="preserve">BISS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mabel Lake</t>
   </si>
   <si>
@@ -230,27 +245,30 @@
     <t xml:space="preserve">Moyie Lake</t>
   </si>
   <si>
+    <t xml:space="preserve">Nine Bay Lake</t>
+  </si>
+  <si>
     <t xml:space="preserve">Norbury Lake</t>
   </si>
   <si>
+    <t xml:space="preserve">Norbury Lakes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Okanagan Lake</t>
   </si>
   <si>
+    <t xml:space="preserve">Okanagan lake</t>
+  </si>
+  <si>
     <t xml:space="preserve">Osoyoos Lake</t>
   </si>
   <si>
     <t xml:space="preserve">Otter Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Paul Lake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pend dOreille River</t>
   </si>
   <si>
-    <t xml:space="preserve">Peter-Hope</t>
-  </si>
-  <si>
     <t xml:space="preserve">Premier Lake</t>
   </si>
   <si>
@@ -260,13 +278,10 @@
     <t xml:space="preserve">Revelstoke Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Roche Lake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rosen Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Seton Lake</t>
+    <t xml:space="preserve">Salmo River</t>
   </si>
   <si>
     <t xml:space="preserve">Sheridan Lake</t>
@@ -275,6 +290,12 @@
     <t xml:space="preserve">Shuswap Lake</t>
   </si>
   <si>
+    <t xml:space="preserve">Okanagan, Thompson-Nicola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSISS, CSISS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Silver Lake</t>
   </si>
   <si>
@@ -290,15 +311,12 @@
     <t xml:space="preserve">Slocan River</t>
   </si>
   <si>
+    <t xml:space="preserve">St. Mary Lake</t>
+  </si>
+  <si>
     <t xml:space="preserve">St. Marys Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Stump Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summit Lake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Surveyors Lake</t>
   </si>
   <si>
@@ -308,16 +326,13 @@
     <t xml:space="preserve">Suzanne Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Swan Lake</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tie Lake</t>
   </si>
   <si>
     <t xml:space="preserve">Trout Lake</t>
   </si>
   <si>
-    <t xml:space="preserve">Tunkwa Lake</t>
+    <t xml:space="preserve">Upper Arrow Lake</t>
   </si>
   <si>
     <t xml:space="preserve">Upper Kettle River</t>
@@ -327,9 +342,6 @@
   </si>
   <si>
     <t xml:space="preserve">Wasa Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whatshan Lake</t>
   </si>
   <si>
     <t xml:space="preserve">White Lake</t>
@@ -737,24 +749,24 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -762,27 +774,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -790,13 +802,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -804,13 +816,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -818,13 +830,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -835,7 +847,7 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>30</v>
@@ -855,7 +867,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -863,10 +875,10 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -877,24 +889,24 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -902,13 +914,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -916,13 +928,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -930,13 +942,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -947,10 +959,10 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -964,7 +976,7 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -975,10 +987,10 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -986,13 +998,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -1000,13 +1012,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -1014,13 +1026,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -1028,13 +1040,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -1042,10 +1054,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
         <v>6</v>
@@ -1056,13 +1068,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1070,13 +1082,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1084,13 +1096,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -1098,13 +1110,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -1112,13 +1124,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -1126,13 +1138,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -1140,13 +1152,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -1154,13 +1166,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -1168,13 +1180,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1182,13 +1194,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1196,13 +1208,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -1210,13 +1222,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -1224,13 +1236,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -1238,13 +1250,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -1252,13 +1264,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -1266,13 +1278,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -1280,13 +1292,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -1294,13 +1306,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -1308,13 +1320,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -1322,13 +1334,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -1336,13 +1348,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -1350,13 +1362,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -1364,13 +1376,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1378,13 +1390,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -1392,13 +1404,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -1406,13 +1418,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -1420,13 +1432,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1434,13 +1446,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1448,13 +1460,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1462,13 +1474,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1476,13 +1488,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1490,13 +1502,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1504,13 +1516,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1518,13 +1530,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1532,13 +1544,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1546,13 +1558,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -1560,13 +1572,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -1574,27 +1586,27 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -1602,13 +1614,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -1616,13 +1628,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -1630,13 +1642,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -1644,13 +1656,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -1658,13 +1670,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -1672,13 +1684,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -1686,13 +1698,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -1700,13 +1712,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -1714,13 +1726,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -1728,13 +1740,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -1742,13 +1754,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B77" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -1756,13 +1768,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -1770,13 +1782,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -1784,13 +1796,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -1798,13 +1810,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -1812,7 +1824,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
         <v>5</v>
@@ -1826,13 +1838,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B83" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -1840,13 +1852,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -1854,13 +1866,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -1868,13 +1880,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -1882,13 +1894,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
